--- a/samples/ss_grati_ingest.xlsx
+++ b/samples/ss_grati_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,19 +692,16 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>IBT 1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -730,7 +717,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -777,15 +763,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -801,7 +783,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -848,15 +829,11 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -872,7 +849,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -901,31 +877,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -954,19 +920,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -982,7 +940,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1011,35 +968,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>seksi A</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1068,31 +1016,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1121,19 +1059,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1149,7 +1079,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1178,19 +1107,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1206,7 +1127,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1235,31 +1155,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1288,19 +1198,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1316,7 +1218,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1345,31 +1246,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1398,19 +1289,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1426,7 +1309,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1455,31 +1337,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1508,19 +1380,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1536,7 +1400,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1565,31 +1428,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1618,19 +1471,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1646,7 +1491,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1675,19 +1519,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1703,7 +1539,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1732,19 +1567,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1760,7 +1587,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1789,31 +1615,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1860,15 +1676,11 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1884,7 +1696,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1931,15 +1742,11 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1955,7 +1762,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1984,19 +1790,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2012,7 +1810,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2041,31 +1838,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2094,31 +1881,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2147,19 +1924,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2175,7 +1944,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2204,31 +1972,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2275,27 +2033,21 @@
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2342,27 +2094,21 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2409,27 +2155,21 @@
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2458,31 +2198,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2511,31 +2241,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2582,15 +2302,11 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2606,7 +2322,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2653,15 +2368,11 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2677,7 +2388,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2706,31 +2416,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2759,19 +2459,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -2787,7 +2479,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2816,31 +2507,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2869,31 +2550,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2922,31 +2593,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2975,19 +2636,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3003,7 +2656,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3032,31 +2684,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3085,19 +2727,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3113,7 +2747,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3142,19 +2775,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -3170,7 +2795,6 @@
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3199,35 +2823,26 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>seksi A/B</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3256,31 +2871,21 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3309,17 +2914,11 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>batas ke Subsistem Kediri</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -3335,13 +2934,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3448,7 +3045,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTA Sutami</t>
@@ -3469,7 +3065,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -3483,8 +3078,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3501,13 +3094,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Outlet PLTA Wlingi</t>
@@ -3528,7 +3119,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>1</v>
       </c>
@@ -3542,8 +3132,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3560,13 +3148,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Outlet PLTA Sengguruh</t>
@@ -3587,7 +3173,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>1</v>
       </c>
@@ -3601,8 +3186,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3619,13 +3202,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Outlet PLTA Selorejo</t>
@@ -3646,7 +3227,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>1</v>
       </c>
@@ -3660,8 +3240,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3678,7 +3256,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3709,7 +3286,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -3723,8 +3299,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3741,13 +3315,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Gedangan - Probolinggo</t>
@@ -3768,7 +3340,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -3782,8 +3353,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3800,13 +3369,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Gedangan - Rejoso</t>
@@ -3827,7 +3394,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -3841,8 +3407,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3859,7 +3423,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3890,7 +3453,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -3904,8 +3466,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3922,7 +3482,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3953,7 +3512,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -3967,8 +3525,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -3985,13 +3541,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>SUTT PIER - Purwosari</t>
@@ -4012,7 +3566,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -4026,8 +3579,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4044,7 +3595,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4075,7 +3625,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -4089,8 +3638,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4107,13 +3654,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>SUTT Bangil - Bacukiro</t>
@@ -4134,7 +3679,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -4148,8 +3692,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4166,7 +3708,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4197,7 +3738,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -4211,8 +3751,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4229,13 +3767,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Bangil - Pakis</t>
@@ -4256,7 +3792,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -4270,8 +3805,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4288,7 +3821,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4319,7 +3851,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -4333,8 +3864,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4351,7 +3880,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4382,7 +3910,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -4396,8 +3923,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4414,13 +3939,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT KIS - Ngeprogo</t>
@@ -4441,7 +3964,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -4455,8 +3977,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4473,7 +3993,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4504,7 +4023,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -4518,8 +4036,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4536,7 +4052,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4567,7 +4082,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -4581,8 +4095,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4599,7 +4111,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4630,7 +4141,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -4644,8 +4154,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4662,13 +4170,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>SUTT Blimbing Kandang - Kebonagung</t>
@@ -4689,7 +4195,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -4703,8 +4208,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4721,13 +4224,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>SUTT Lawang - Kebonagung</t>
@@ -4748,7 +4249,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>2</v>
       </c>
@@ -4762,8 +4262,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4780,13 +4278,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>SUTT Purwosari - Sekarlangit</t>
@@ -4807,7 +4303,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>2</v>
       </c>
@@ -4821,8 +4316,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4839,7 +4332,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4870,7 +4362,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>2</v>
       </c>
@@ -4884,8 +4375,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4902,7 +4391,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4933,7 +4421,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>2</v>
       </c>
@@ -4947,8 +4434,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -4965,13 +4450,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>SUTT 70 kV Kebonagung - Sengguruh</t>
@@ -4992,7 +4475,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>2</v>
       </c>
@@ -5006,8 +4488,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5024,7 +4504,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -5055,7 +4534,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>2</v>
       </c>
@@ -5069,8 +4547,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5087,7 +4563,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -5118,7 +4593,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -5132,8 +4606,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5150,13 +4622,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>SUTT 70 kV Sekarlangit - Pulahan</t>
@@ -5177,7 +4647,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -5191,8 +4660,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5209,7 +4676,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -5240,7 +4706,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -5254,8 +4719,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5272,13 +4735,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>SUTT 70 kV Pulahan - Balebang</t>
@@ -5299,7 +4760,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -5313,8 +4773,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5331,13 +4789,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>SUTT 70 kV Mendalan - Siman</t>
@@ -5358,7 +4814,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>2</v>
       </c>
@@ -5372,8 +4827,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5390,13 +4843,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>SUTT 70 kV Siman - Sukorejo (arah SS Kediri)</t>
@@ -5417,7 +4868,6 @@
           <t>70 kV</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -5431,8 +4881,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>Jawa Timur</t>
@@ -5449,7 +4897,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5533,7 +4980,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034,COD di 2026 (informasi terupdate COD Juni 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). JangkaMenengah: 6. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 7. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 8. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 9. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2026 (informasi terupdate COD Juni 2026). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menengah: 6. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 7. Pembangunan PLTP Arjuna Welirang dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2032). 8. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 9. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5000,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] PembebananSUTT 150 kV Grati-Gondang wetan &gt;90% sehingga sudahtidakmemenuhi kriteria N-1. PembebananSUTT 150 kV Grati-Pier tidak optimal,karenabeban lebih cenderung melewatiSUTT 150 kV Grati-Gondangwetan</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Grati-Gondang wetan &gt;90% sehingga sudah tidak memenuhi kriteria N-1. Pembebanan SUTT 150 kV Grati-Pier tidak optimal,karena beban lebih cenderung melewati SUTT 150 kV Grati-Gondangwetan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5568,7 +5015,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menegah : 6. Percepatan Rekonduktoring SUTT 150 kV Grati- Gondangwetan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029). Jangka Panjang: 7. Pembangunan PLTP Gunung Songgoriti dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 8. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 9. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menegah : 6. Percepatan Rekonduktoring SUTT 150 kV Grati- Gondangwetan. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2029). Jangka Panjang : 7. Pembangunan PLTP Gunung Songgoriti dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 8. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 9. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5050,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - Usulan / Solusi 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkatesdan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Panjang : 6. Pembangunan PLTP Gunung Songgoriti dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - Usulan / Solusi 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 5. Pembangunan PLTS 150 kV dan BESS dengan total 100 MW di Pasuruan (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Panjang : 6. Pembangunan PLTP Gunung Songgoriti dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5070,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kVPier-Bangil 1&amp;2 &gt;75% sehingga tidak memenuhi kriteriaN-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Pier-Bangil 1&amp;2 &gt;75% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5638,7 +5085,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di2025 (informasi terupdate COD Juni 2026)). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). JangkaMenengah: Usulan / Solusi 5. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 6. Pembangunan PLTP Songgoriti dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 7. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 8. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Percepatan pembangunan GITET 500 kV Watudodol/Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 3. Pembangunan SUTET 500 kV Paiton - Kalipuro. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026) Mundur COD Desember 2028. 4. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Menengah: Usulan / Solusi 5. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2031). Jangka Panjang : 6. Pembangunan PLTP Songgoriti dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 7. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033). 8. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5105,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Bangil-Bangil New 1,2 &gt;80% sehingga tidak memenuhi kriteria N-1</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Bangil -Bangil New 1,2 &gt;80% sehingga tidak memenuhi kriteria N-1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5668,12 +5115,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT 150 kV Bangil - New Bangil dengan total target sebesar135 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Bangil - New Bangil dengan total target sebesar 135 MW (Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Panjang : 3. Pembangunan PLTP Songgoriti dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Jangka Panjang : 3. Pembangunan PLTP Songgoriti dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5150,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS SUTT 150 kV Bangil-Lawang dan Bangil- Bulukandang dengan total target sebesar135 MW (Berdasarkan Deklarasi ROB Mei Tahun 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Bangil-Lawang dan Bangil- Bulukandang dengan total target sebesar 135 MW (Berdasarkan Deklarasi ROB Mei Tahun 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GITET 500 kV Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Normalisasi Doble phi SUTT 150 kV Bulukandang-Bangil- Lawang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 3. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi JangkaPanjang: 4. Pembangunan PLTP Songgoriti dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Normalisasi Doble phi SUTT 150 kV Bulukandang -Bangil- Lawang. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2027). 3. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi Jangka Panjang: 4. Pembangunan PLTP Songgoriti dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5175,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Bangil-KIS-New Porong &gt;60% sehingga tidak memenuhi kriteria N-1, jika pembebanan ditambah dengan bebanSidoarjodenga n konfigurasi single phi</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Bangil-KIS-New Porong &gt;60% sehingga tidak memenuhi kriteria N-1, jika pembebanan ditambah dengan beban Sidoarjodenga n konfigurasi single phi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5738,12 +5185,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SudahterpasangOLSS UTT150 kV Bangil-KIS- New Porong dengan total target sebesar 144 MW (Berdasarkan Deklarasi ROB Mei Tahun 2026)</t>
+          <t>SudahterpasangOLS S UTT 150 kV Bangil-KIS- New Porong dengan total target sebesar 144 MW (Berdasarkan Deklarasi ROB Mei Tahun 2026)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2.Pembangunan SUTT 150 kV Ngoro - New Porong (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
+          <t>Jangka Pendek : 1. Pembangunan GITET 500 kV Bangil dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di 2025 (informasi terupdate COD Juni 2026)). 2. Pembangunan SUTT 150 kV Ngoro - New Porong (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5210,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] GI 150 kV PLTASutami hanyasingleBusbar</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV PLTA Sutami hanya singleBusbar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5778,7 +5225,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Usulan baru Penambahan Busbar ke-2 (Double Busbar) di GI 150 kV PLTA Sutami dan Kopel Busbar (Sesuai kajian operasi diusulkan COD di Tahun 2026)</t>
+          <t>Jangka Pendek : Usulan baru Penambahan Busbar ke-2 (Double Busbar) di GI 150 kV PLTA Sutami dan Kopel Busbar (Sesuai kajian operasi diusulkan COD di Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5245,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] SUTT 150 kV Wlingi- Sutami hanya beroperasi1sirkitdan sudahberbebandiatas 95%</t>
+          <t>[BELUM_DITETAPKAN] SUTT 150 kV Wlingi- Sutami hanya beroperasi 1sirkitdan sudah berbeban diatas 95%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5813,7 +5260,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025-2034, COD Tahun 2026). 2.Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025-2034, COD Tahun 2026). 3.Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi 4.Usulan agar Unit Distribusi membangun jaringan 20 kV baru agar beban 70kV di GI sekitar GI Tulungagung, GI PLTA Tulungagung, GI Blitar dan GI Wlingi bisa dialihkan ke GI 150 kV yang baru (GI New Tulungagung dan GI New Wlingi) (diusulkan COD masuk di 2026). 5.Pembangunan SUTT 150 kV PLTA Wlingi - Wlingi II. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 6.Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025-2034, COD Tahun 2026). 7.Pembangunan SUTT 150 kV Sutami-Wlingi line ke 2 &amp; 3 (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah : 8.Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025-2034, COD Tahun 2031). Jangka Panjang : 9.Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025-2034, COD Tahun 2033). 10.Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025-2034, COD Tahun 2033)</t>
+          <t>Jangka Pendek : 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi 4. Usulan agar Unit Distribusi membangun jaringan 20 kV baru agar beban 70kV di GI sekitar GI Tulungagung, GI PLTA Tulungagung, GI Blitar dan GI Wlingi bisa dialihkan ke GI 150 kV yang baru (GI New Tulungagung dan GI New Wlingi) (diusulkan COD masuk di 2026). 5. Pembangunan SUTT 150 kV PLTA Wlingi - Wlingi II. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 6. Pembangunan PLTS Karangkates dan Line bay terkait (Berdasarkan RUPTL 2025 -2034, COD Tahun 2026). 7. Pembangunan SUTT 150 kV Sutami-Wlingi line ke 2 &amp; 3 (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028). Jangka Menengah : 8. Pembangunan PLTB 150 kV dengan Total 100 MW Tahap I di Blitar (Berdasarkan RUPTL 2025 -2034, COD Tahun 2031). Jangka Panjang : 9. Pembangunan PLTB 150 kV dengan Total 200 MW Tahap II di Blitar (Berdasarkan RUPTL 2025 -2034, COD Tahun 2033). 10. Pembangunan PLTB 150 kV dengan Total 200 MW di Malang (Berdasarkan RUPTL 2025 -2034, COD Tahun 2033)</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5280,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] GI 150 kV dan 70 kV PLTA Wlingi hanya singleBusbar</t>
+          <t>[BELUM_DITETAPKAN] GI 150 kV dan 70 kV PLTA Wlingi hanya single Busbar</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5848,7 +5295,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Usulan baru penambahan Busbar ke-2 (Double Busbar) dan kopel Busbar di GI 150 kV dan 70 kV Wlingi. (Sesuai kajian operasi diusulkan COD di Tahun 2026)</t>
+          <t>Jangka Pendek : Usulan baru penambahan Busbar ke-2 (Double Busbar) dan kopel Busbar di GI 150 kV dan 70 kV Wlingi. (Sesuai kajian operasi diusulkan COD di Tahun 2026)</t>
         </is>
       </c>
     </row>
@@ -5878,12 +5325,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1. Penjadwalan pekerjaan IBT dilakukan pada saat musim basah/PLTA bisa beroperasi. 2. Dilakukan manuver beban yang cukup kompleks melibatkan SS 70 kV Wlingi,Banaran,dan Ponorogo serta manuver beban 20 kV oleh UP2D Jatim. 3. Hanya dapat dilakukan pada periode musim hujan untuk kesiapan PLTAWlingi,Tulunga gung, Lodoyo (20 kV), dan Wonorejo (20 kV)</t>
+          <t>1. Penjadwalan pekerjaan IBT dilakukan pada saat musim basah/PLTA bisa beroperasi. 2. Dilakukan manuver beban yang cukup kompleks melibatkan SS 70 kV Wlingi,Banaran, dan Ponorogo serta manuver beban 20 kV oleh UP2D Jatim. 3. Hanya dapat dilakukan pada periode musim hujan untuk kesiapan PLTAWlingi,Tulunga gung, Lodoyo (20 kV), dan Wonorejo (20 kV)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Percepatan Pembangunan GI 150 kV Blitar Baru dan Line terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
+          <t>Jangka Pendek : 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 4. Percepatan Pembangunan GI 150 kV Blitar Baru dan Line terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5365,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi 4. Usulan agar Unit Distribusi membangun jaringan 20 kV baru agar beban 70kV di GI sekitar GI Tulungagung, GI PLTA Tulungagung, GI Blitar dan GI Wlingi bisa dialihkan ke GI 150 kV yang baru (GI New Tulungagung dan GI New Wlingi) (diusulkan COD masuk di 2026). 5. Percepatan Pembangunan GI 150 kV Blitar Baru dan Line terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
+          <t>Jangka Pendek : 1. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Penambahan Trafo Distribusi 150/20 kV ke-2 kapasitas 60 MVA di GI 150 kV New Wlingi. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 3. Penambahan Trafo Distribusi 150/20 kV ke-3 kapasitas 60 MVA di GI 150 kV New Tulungagung. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). Usulan / Solusi 4. Usulan agar Unit Distribusi membangun jaringan 20 kV baru agar beban 70kV di GI sekitar GI Tulungagung, GI PLTA Tulungagung, GI Blitar dan GI Wlingi bisa dialihkan ke GI 150 kV yang baru (GI New Tulungagung dan GI New Wlingi) (diusulkan COD masuk di 2026). 5. Percepatan Pembangunan GI 150 kV Blitar Baru dan Line terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2028)</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5385,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 70kV Kebonagung- Turen dan Kebonagung- Sengguruh &gt;80% sehingga tidak memenuhi kriteria N- 1. Pembebanan tidak seimbang karena konfigurasi single phi di SUTT 70 kV Sengguruh- Gampingan-Turen- KebonAgung</t>
+          <t>[N-1] Pembebanan SUTT 70kV Kebonagung- Turen dan Kebonagung- Sengguruh &gt;80% sehingga tidak memenuhi kriteria N- 1. Pembebanan tidak seimbang karena konfigurasi single phi di SUTT 70 kV Sengguruh- Gampingan-Turen- Kebon Agung</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5953,7 +5400,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JangkaPendek: 1.Usulan Double Phi GI 70 kV Kebonagung T/L bay Sengguruh dan T/L bay Turen (diusulkan COD Tahun 2026). Jangka Panjang : 2.PembangunanGI150 kV Turen Baru dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di luar periode RUPTL). 3.Pembangunan GI 150 kV PLTA Karangkates dan Line Bay Terkait. (Berdasarkan RUPTL 2025 - 2034, COD di luar periode RUPTL)</t>
+          <t>Jangka Pendek: 1. Usulan Double Phi GI 70 kV Kebonagung T/L bay Sengguruh dan T/L bay Turen (diusulkan COD Tahun 2026). Jangka Panjang : 2. PembangunanGI150 kV Turen Baru dan Line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD di luar periode RUPTL). 3. Pembangunan GI 150 kV PLTA Karangkates dan Line Bay Terkait. (Berdasarkan RUPTL 2025 - 2034, COD di luar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5430,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1. Sudah terpasang OLS di SUTT Kebonagung- Polehan dengan total target9 MW (berdasarkan Deklasarasi Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
+          <t>1. Sudah terpasang OLS di SUTT Kebonagung- Polehan dengan total target 9 MW (berdasarkan Deklasarasi Berdasarkan Deklarasi ROB Mei 2026). 2. Pekerjaan dilakukan saat beban rendah</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JangkaPendek: Pembangunan GI 150 kV New Polehan dan Line bay Terkait. (Berdasarkan RUPTL 2025-2034, COD di luar periode RUPTL)</t>
+          <t>Jangka Pendek: Pembangunan GI 150 kV New Polehan dan Line bay Terkait. (Berdasarkan RUPTL 2025 -2034, COD di luar periode RUPTL)</t>
         </is>
       </c>
     </row>
@@ -6043,7 +5490,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di Subsistem Grati pada GI 150 kVSutami, GIWlingidan GI 70 kV Gampingan</t>
+          <t>[BELUM_DITETAPKAN] Terjadi Drop tegangan di Subsistem Grati pada GI 150 kV Sutami, GI Wlingi dan GI 70 kV Gampingan</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6058,7 +5505,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Jangka Pendek : 1. Pembangunan PLTS Karangkatesdan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Pemasangan kapasitor pada GI Sengkaling (50 MVAR). Update UIT JBM COD 2027. 3. Pemasangan Kapasitor MVAR di GI Sengguruh (10 MVAR). Update UIT JBM COD 2027</t>
+          <t>Jangka Pendek : 1. Pembangunan PLTS Karangkates dan line bay terkait. (Berdasarkan RUPTL 2025 - 2034, COD Tahun 2026). 2. Pemasangan kapasitor pada GI Sengkaling (50 MVAR). Update UIT JBM COD 2027. 3. Pemasangan Kapasitor MVAR di GI Sengguruh (10 MVAR). Update UIT JBM COD 2027</t>
         </is>
       </c>
     </row>
